--- a/data/reports/2024-12-02/2024-12-02_duplicates.xlsx
+++ b/data/reports/2024-12-02/2024-12-02_duplicates.xlsx
@@ -185,7 +185,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004139</t>
+    <t>RMD0009352</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -201,28 +201,28 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>800-7096314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004139</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
     <t>800-709-6314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009352</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>800-7096314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008972</t>
@@ -261,7 +261,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009084</t>
+    <t>RMD0009205</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,12 +318,6 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
-  </si>
-  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -346,7 +340,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
+    <t>RMD0009084</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -409,7 +409,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004724</t>
+    <t>RMD0005819</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -419,16 +419,16 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>4109121000</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004724</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005819</t>
-  </si>
-  <si>
-    <t>4109121000</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004849</t>
@@ -493,10 +493,37 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>1250 E Hallandale Beach Blvd
+Hallandale FL 33009</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -528,33 +555,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>1250 E Hallandale Beach Blvd
-Hallandale FL 33009</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005139</t>
@@ -711,7 +711,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -721,6 +721,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -739,13 +745,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005569</t>
+    <t>RMD0005461</t>
   </si>
   <si>
     <t>Valstarr Asia</t>
@@ -755,25 +755,10 @@
 Valley Center CA 92082</t>
   </si>
   <si>
+    <t>0031217672</t>
+  </si>
+  <si>
     <t>Vincent W. Kahn</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Systems Admin</t>
-  </si>
-  <si>
-    <t>'+13213288217</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005461</t>
-  </si>
-  <si>
-    <t>0031217672</t>
   </si>
   <si>
     <t>MANAGER</t>
@@ -793,7 +778,22 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0005569</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Systems Admin</t>
+  </si>
+  <si>
+    <t>'+13213288217</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -806,25 +806,25 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
+    <t>RMD0005585</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -838,6 +838,28 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
+  </si>
+  <si>
+    <t>Paul Joncas</t>
+  </si>
+  <si>
+    <t>Operatopms</t>
+  </si>
+  <si>
+    <t>187 Plymouth Avenue
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005574</t>
+  </si>
+  <si>
     <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
   </si>
   <si>
@@ -845,29 +867,20 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005585</t>
-  </si>
-  <si>
-    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
-  </si>
-  <si>
-    <t>Paul Joncas</t>
-  </si>
-  <si>
-    <t>Operatopms</t>
-  </si>
-  <si>
-    <t>187 Plymouth Avenue
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+    <t>RMD0006284</t>
+  </si>
+  <si>
+    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
+  Islamabad, Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -877,9 +890,6 @@
 federal 46000 Islamabad, Pakistan</t>
   </si>
   <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
     <t>Umair Hassan</t>
   </si>
   <si>
@@ -890,16 +900,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006284</t>
-  </si>
-  <si>
-    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
-  Islamabad, Pakistan</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008125</t>
@@ -931,7 +931,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
+    <t>RMD0007575</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -944,16 +944,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007626</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007575</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007716</t>
+    <t>RMD0007696</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -963,16 +963,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007716</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -982,6 +982,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -997,13 +1003,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
+    <t>RMD0008393</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1011,6 +1011,12 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1028,13 +1034,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008393</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1044,12 +1044,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1057,7 +1051,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008610</t>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1067,43 +1067,49 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008610</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008759</t>
+    <t>RMD0008756</t>
   </si>
   <si>
     <t>573 Ocean Blvd
 Hampton NH 03842</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008759</t>
+  </si>
+  <si>
     <t>Jeffrey D Houston</t>
   </si>
   <si>
@@ -1116,13 +1122,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008756</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008755</t>
+    <t>RMD0008798</t>
   </si>
   <si>
     <t>Aspire Holdings Group LLC</t>
@@ -1135,30 +1135,30 @@
     <t>AspirePBX</t>
   </si>
   <si>
+    <t>CP Short</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>6023888700</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008755</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008798</t>
-  </si>
-  <si>
-    <t>CP Short</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>6023888700</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0008787</t>
   </si>
   <si>
@@ -1189,7 +1189,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1199,16 +1199,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -6343,9 +6343,15 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1" t="s">
         <v>58</v>
       </c>
@@ -6403,15 +6409,9 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>58</v>
       </c>
@@ -6586,9 +6586,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>34</v>
@@ -6599,14 +6601,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6633,7 +6637,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6642,13 +6646,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>34</v>
@@ -6659,9 +6661,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6680,41 +6680,55 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R13" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6726,46 +6740,32 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6791,54 +6791,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6855,33 +6841,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -7000,16 +7000,28 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="M19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R19" s="1" t="s">
         <v>26</v>
       </c>
@@ -7017,16 +7029,16 @@
         <v>26</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="1">
         <v>25462672</v>
@@ -7046,28 +7058,16 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
         <v>26</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -7320,31 +7320,27 @@
       <c r="O25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B26" s="1">
         <v>27710730</v>
@@ -7353,7 +7349,7 @@
         <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -7365,37 +7361,41 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="N26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
         <v>169</v>
       </c>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>34</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>34</v>
@@ -7859,48 +7859,34 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B36" s="1">
         <v>31124688</v>
@@ -7919,25 +7905,39 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="M36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R36" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1" t="s">
@@ -7963,48 +7963,54 @@
       <c r="F37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J37" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B38" s="1">
         <v>31217029</v>
@@ -8021,26 +8027,20 @@
       <c r="F38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>27</v>
@@ -8050,16 +8050,16 @@
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8088,33 +8088,45 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="M39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+        <v>244</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1">
         <v>31294614</v>
@@ -8134,36 +8146,24 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>189</v>
-      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1" t="s">
@@ -8195,42 +8195,48 @@
       <c r="H41" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="M41" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U41" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V41" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1">
         <v>31356652</v>
@@ -8251,18 +8257,14 @@
         <v>255</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L42" s="1" t="s">
         <v>263</v>
       </c>
+      <c r="I42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
         <v>264</v>
       </c>
@@ -8270,24 +8272,22 @@
         <v>27</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
         <v>265</v>
       </c>
@@ -8309,55 +8309,49 @@
       <c r="F43" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>270</v>
-      </c>
+      <c r="G43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q43" s="1"/>
       <c r="R43" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B44" s="1">
         <v>31392434</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>34</v>
@@ -8365,33 +8359,39 @@
       <c r="F44" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="M44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="Q44" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8439,7 +8439,7 @@
         <v>281</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>33</v>
@@ -8529,9 +8529,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -8575,7 +8573,9 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -8613,15 +8613,9 @@
       <c r="F49" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -8665,9 +8659,15 @@
       <c r="F50" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="G50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -8706,55 +8706,41 @@
         <v>300</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B52" s="1">
         <v>31445216</v>
@@ -8766,32 +8752,46 @@
         <v>300</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
+        <v>300</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R52" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1" t="s">
@@ -8820,43 +8820,33 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>313</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B54" s="1">
         <v>31455868</v>
@@ -8876,24 +8866,34 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
+        <v>314</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+      <c r="Q54" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8926,7 +8926,7 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -8943,12 +8943,12 @@
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" s="1">
         <v>31457815</v>
@@ -8972,7 +8972,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
-        <v>322</v>
+        <v>40</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -9014,33 +9014,45 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M57" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+        <v>326</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
+      <c r="Q57" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R57" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B58" s="1">
         <v>31475270</v>
@@ -9055,50 +9067,40 @@
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="I58" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>332</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="Q58" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:22">
       <c r="A59" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B59" s="1">
         <v>31475270</v>
@@ -9113,13 +9115,11 @@
         <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -9156,53 +9156,41 @@
         <v>338</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B61" s="1">
         <v>31485048</v>
@@ -9212,32 +9200,44 @@
         <v>338</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
+        <v>338</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R61" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9258,43 +9258,57 @@
         <v>347</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="M62" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
+        <v>347</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B63" s="1">
         <v>31489362</v>
@@ -9306,48 +9320,34 @@
         <v>347</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>353</v>
-      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
@@ -9397,7 +9397,7 @@
         <v>362</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q64" s="1" t="s">
         <v>33</v>
@@ -9478,49 +9478,39 @@
         <v>369</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1" t="s">
-        <v>368</v>
-      </c>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
-      <c r="M66" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>370</v>
-      </c>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
       <c r="P66" s="1"/>
-      <c r="Q66" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B67" s="1">
         <v>31544182</v>
@@ -9532,30 +9522,40 @@
         <v>369</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>368</v>
+      </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="M67" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
+      <c r="Q67" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R67" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
@@ -9632,7 +9632,7 @@
         <v>380</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>381</v>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>34</v>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>34</v>
@@ -9784,13 +9784,13 @@
         <v>27</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>395</v>
@@ -9852,7 +9852,7 @@
         <v>402</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>31</v>
@@ -10020,10 +10020,10 @@
         <v>420</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>418</v>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>34</v>
@@ -10122,10 +10122,10 @@
         <v>428</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M78" s="1"/>
       <c r="N78" s="1" t="s">
@@ -10240,10 +10240,10 @@
         <v>443</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>441</v>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>34</v>
@@ -10296,7 +10296,7 @@
         <v>448</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>449</v>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>34</v>
@@ -10360,7 +10360,7 @@
         <v>457</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L82" s="1"/>
       <c r="M82" s="1" t="s">
@@ -10405,7 +10405,7 @@
         <v>34</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -10511,7 +10511,7 @@
         <v>59</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M85" s="1" t="s">
         <v>472</v>
@@ -10524,7 +10524,7 @@
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>34</v>
@@ -10566,7 +10566,7 @@
         <v>478</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L86" s="1"/>
       <c r="M86" s="1" t="s">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="P87" s="1"/>
       <c r="Q87" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>34</v>
@@ -10726,10 +10726,10 @@
         <v>493</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>491</v>
@@ -10787,7 +10787,7 @@
         <v>500</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>497</v>
@@ -10882,7 +10882,7 @@
         <v>508</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>509</v>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="P92" s="1"/>
       <c r="Q92" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R92" s="1" t="s">
         <v>34</v>
@@ -10934,10 +10934,10 @@
         <v>513</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>514</v>
@@ -11135,7 +11135,7 @@
         <v>34</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>28</v>
@@ -11181,7 +11181,7 @@
         <v>34</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>34</v>
@@ -11288,13 +11288,13 @@
         <v>27</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>545</v>
@@ -11303,7 +11303,7 @@
         <v>59</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>544</v>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>34</v>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>26</v>
@@ -11424,7 +11424,7 @@
         <v>562</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L102" s="1" t="s">
         <v>563</v>
@@ -11528,7 +11528,7 @@
         <v>571</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>572</v>
@@ -11694,7 +11694,7 @@
         <v>588</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>589</v>
@@ -11872,7 +11872,7 @@
         <v>607</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" s="1" t="s">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="P110" s="1"/>
       <c r="Q110" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R110" s="1" t="s">
         <v>26</v>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P112" s="1"/>
       <c r="Q112" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>34</v>
@@ -12055,7 +12055,7 @@
         <v>59</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>629</v>
@@ -12152,7 +12152,7 @@
         <v>639</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>640</v>
@@ -12256,10 +12256,10 @@
         <v>652</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>650</v>
@@ -12314,7 +12314,7 @@
         <v>658</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>659</v>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R118" s="1" t="s">
         <v>34</v>
@@ -12422,7 +12422,7 @@
         <v>669</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>670</v>
@@ -12485,7 +12485,7 @@
         <v>678</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>674</v>
@@ -12538,10 +12538,10 @@
         <v>683</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M122" s="1"/>
       <c r="N122" s="1" t="s">
@@ -12598,10 +12598,10 @@
         <v>690</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M123" s="1" t="s">
         <v>689</v>
@@ -12656,10 +12656,10 @@
         <v>696</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M124" s="1" t="s">
         <v>695</v>
@@ -12714,7 +12714,7 @@
         <v>702</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>703</v>
@@ -12770,10 +12770,10 @@
         <v>708</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>709</v>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R126" s="1" t="s">
         <v>34</v>
@@ -12832,7 +12832,7 @@
         <v>715</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L127" s="1" t="s">
         <v>381</v>
@@ -12881,7 +12881,7 @@
         <v>34</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>28</v>
@@ -12905,7 +12905,7 @@
         <v>719</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O128" s="1" t="s">
         <v>722</v>
@@ -12970,7 +12970,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>34</v>
@@ -13012,10 +13012,10 @@
         <v>733</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>731</v>
@@ -13071,7 +13071,7 @@
         <v>740</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>737</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R132" s="1" t="s">
         <v>34</v>
@@ -13246,10 +13246,10 @@
         <v>759</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M134" s="1" t="s">
         <v>758</v>
@@ -13398,13 +13398,13 @@
         <v>27</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>776</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J137" s="1" t="s">
         <v>777</v>
@@ -13413,7 +13413,7 @@
         <v>778</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>775</v>
@@ -13520,10 +13520,10 @@
         <v>789</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>790</v>
@@ -13623,7 +13623,7 @@
         <v>34</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
@@ -13641,14 +13641,14 @@
         <v>803</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O141" s="1" t="s">
         <v>804</v>
       </c>
       <c r="P141" s="1"/>
       <c r="Q141" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R141" s="1" t="s">
         <v>34</v>
@@ -13780,7 +13780,7 @@
         <v>816</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>817</v>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="P144" s="1"/>
       <c r="Q144" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R144" s="1" t="s">
         <v>34</v>
@@ -13897,7 +13897,7 @@
         <v>59</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M146" s="1"/>
       <c r="N146" s="1" t="s">
@@ -13968,7 +13968,7 @@
         <v>840</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R147" s="1" t="s">
         <v>26</v>
@@ -14193,7 +14193,7 @@
         <v>553</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M152" s="1"/>
       <c r="N152" s="1" t="s">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R152" s="1" t="s">
         <v>34</v>
@@ -14249,7 +14249,7 @@
         <v>866</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M153" s="1"/>
       <c r="N153" s="1" t="s">
@@ -14360,7 +14360,7 @@
         <v>880</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L155" s="1" t="s">
         <v>881</v>
@@ -14408,7 +14408,7 @@
         <v>27</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>26</v>
@@ -14507,7 +14507,7 @@
         <v>34</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>28</v>
@@ -14531,7 +14531,7 @@
         <v>898</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O158" s="1" t="s">
         <v>899</v>
@@ -14572,7 +14572,7 @@
         <v>27</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>903</v>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R163" s="1" t="s">
         <v>34</v>
@@ -14957,7 +14957,7 @@
         <v>34</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
@@ -14966,14 +14966,14 @@
         <v>942</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L166" s="1" t="s">
         <v>189</v>
       </c>
       <c r="M166" s="1"/>
       <c r="N166" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O166" s="1" t="s">
         <v>943</v>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>34</v>
@@ -15283,7 +15283,7 @@
         <v>975</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>976</v>
@@ -15338,7 +15338,7 @@
         <v>981</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L173" s="1" t="s">
         <v>31</v>
@@ -15450,10 +15450,10 @@
         <v>993</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M175" s="1"/>
       <c r="N175" s="1" t="s">
@@ -15511,7 +15511,7 @@
         <v>59</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>997</v>
@@ -15569,7 +15569,7 @@
         <v>1006</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>1007</v>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="P179" s="1"/>
       <c r="Q179" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>34</v>
@@ -15743,7 +15743,7 @@
         <v>1028</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M180" s="1"/>
       <c r="N180" s="1" t="s">
@@ -15912,13 +15912,13 @@
         <v>27</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>1051</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
@@ -16088,7 +16088,7 @@
         <v>1067</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L186" s="1" t="s">
         <v>1068</v>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="P186" s="1"/>
       <c r="Q186" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>34</v>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="P187" s="1"/>
       <c r="Q187" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R187" s="1" t="s">
         <v>34</v>
@@ -16204,10 +16204,10 @@
         <v>1080</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M188" s="1" t="s">
         <v>1078</v>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="P188" s="1"/>
       <c r="Q188" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R188" s="1" t="s">
         <v>26</v>
@@ -16256,14 +16256,14 @@
         <v>27</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>1084</v>
       </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K189" s="1" t="s">
         <v>59</v>
@@ -16364,13 +16364,13 @@
         <v>27</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>1091</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>34</v>
@@ -16660,10 +16660,10 @@
         <v>1127</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M196" s="1" t="s">
         <v>1128</v>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="P196" s="1"/>
       <c r="Q196" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R196" s="1" t="s">
         <v>34</v>
@@ -16747,7 +16747,7 @@
         <v>34</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G198" s="1"/>
       <c r="H198" s="1"/>
@@ -16765,14 +16765,14 @@
         <v>1137</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O198" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="P198" s="1"/>
       <c r="Q198" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R198" s="1" t="s">
         <v>34</v>
@@ -16872,7 +16872,7 @@
         <v>1149</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L200" s="1" t="s">
         <v>189</v>
@@ -16932,7 +16932,7 @@
         <v>1157</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L201" s="1" t="s">
         <v>189</v>
@@ -16990,7 +16990,7 @@
         <v>1162</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L202" s="1" t="s">
         <v>189</v>
@@ -17050,7 +17050,7 @@
         <v>1168</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L203" s="1" t="s">
         <v>1169</v>
@@ -17106,7 +17106,7 @@
         <v>1175</v>
       </c>
       <c r="K204" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L204" s="1" t="s">
         <v>396</v>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="P206" s="1"/>
       <c r="Q206" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R206" s="1" t="s">
         <v>34</v>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>34</v>
@@ -17338,13 +17338,13 @@
         <v>185</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>1208</v>
@@ -17536,10 +17536,10 @@
         <v>1227</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M211" s="1" t="s">
         <v>1228</v>
@@ -17614,7 +17614,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>34</v>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="P213" s="1"/>
       <c r="Q213" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R213" s="1" t="s">
         <v>34</v>
@@ -17758,7 +17758,7 @@
         <v>1166</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
@@ -17884,7 +17884,7 @@
         <v>1252</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L217" s="1" t="s">
         <v>189</v>
@@ -17953,7 +17953,7 @@
         <v>1265</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>1266</v>
@@ -18013,7 +18013,7 @@
         <v>1273</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M219" s="1" t="s">
         <v>1274</v>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P220" s="1"/>
       <c r="Q220" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R220" s="1" t="s">
         <v>26</v>
@@ -18131,7 +18131,7 @@
         <v>1287</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>1286</v>
@@ -18562,10 +18562,10 @@
         <v>1338</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M228" s="1" t="s">
         <v>1339</v>
@@ -18616,13 +18616,13 @@
         <v>27</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>1345</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>1346</v>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>34</v>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>34</v>
@@ -18824,7 +18824,7 @@
         <v>1372</v>
       </c>
       <c r="K232" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L232" s="1" t="s">
         <v>1373</v>
@@ -19028,7 +19028,7 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R235" s="1" t="s">
         <v>34</v>
@@ -19327,7 +19327,7 @@
         <v>1430</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M240" s="1" t="s">
         <v>1426</v>
@@ -19508,10 +19508,10 @@
         <v>1447</v>
       </c>
       <c r="K243" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M243" s="1" t="s">
         <v>1446</v>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R243" s="1" t="s">
         <v>34</v>
@@ -19568,10 +19568,10 @@
         <v>1453</v>
       </c>
       <c r="K244" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M244" s="1" t="s">
         <v>1452</v>
@@ -19620,22 +19620,22 @@
         <v>27</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>1453</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M245" s="1" t="s">
         <v>1457</v>
@@ -19823,7 +19823,7 @@
         <v>280</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1480</v>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>34</v>
@@ -19885,7 +19885,7 @@
         <v>280</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1480</v>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R249" s="1" t="s">
         <v>34</v>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>34</v>
@@ -20429,7 +20429,7 @@
         <v>1548</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M258" s="1" t="s">
         <v>1544</v>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R258" s="1" t="s">
         <v>34</v>
@@ -20491,7 +20491,7 @@
         <v>1548</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M259" s="1" t="s">
         <v>1554</v>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>34</v>
@@ -20551,7 +20551,7 @@
         <v>553</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1562</v>
@@ -20564,7 +20564,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>34</v>
@@ -20724,13 +20724,13 @@
         <v>27</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>1581</v>
@@ -20812,7 +20812,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>34</v>
@@ -20876,7 +20876,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>34</v>
@@ -20927,7 +20927,7 @@
         <v>740</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1607</v>
@@ -20989,7 +20989,7 @@
         <v>740</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1607</v>
@@ -21053,7 +21053,7 @@
         <v>59</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1619</v>
@@ -21117,7 +21117,7 @@
         <v>59</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1628</v>
@@ -21166,13 +21166,13 @@
         <v>195</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>1635</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>1636</v>
@@ -21196,7 +21196,7 @@
         <v>1640</v>
       </c>
       <c r="Q270" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>34</v>
@@ -21234,13 +21234,13 @@
         <v>195</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>1635</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>1636</v>
@@ -21264,7 +21264,7 @@
         <v>1640</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>34</v>
@@ -21360,13 +21360,13 @@
         <v>27</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>1648</v>
@@ -21439,7 +21439,7 @@
         <v>1329</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M274" s="1" t="s">
         <v>1666</v>
@@ -21452,7 +21452,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>34</v>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>34</v>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="P277" s="1"/>
       <c r="Q277" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R277" s="1" t="s">
         <v>34</v>
@@ -22171,7 +22171,7 @@
         <v>1756</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M286" s="1" t="s">
         <v>1753</v>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P286" s="1"/>
       <c r="Q286" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R286" s="1" t="s">
         <v>34</v>
@@ -22229,7 +22229,7 @@
         <v>1761</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M287" s="1" t="s">
         <v>1753</v>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="P287" s="1"/>
       <c r="Q287" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R287" s="1" t="s">
         <v>34</v>
